--- a/data/trans_orig/P32D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61142</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127620</t>
+          <t>128514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155037</t>
+          <t>155007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73954</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92936</t>
+          <t>92270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209611</t>
+          <t>208051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243360</t>
+          <t>243474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23933</t>
+          <t>24010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191889</t>
+          <t>191571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214654</t>
+          <t>214917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118607</t>
+          <t>118047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135107</t>
+          <t>134947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318398</t>
+          <t>318960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346790</t>
+          <t>346713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>39083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243483</t>
+          <t>243100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264293</t>
+          <t>263790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140108</t>
+          <t>139603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148240</t>
+          <t>148175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389361</t>
+          <t>388392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410164</t>
+          <t>409680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>38588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>48270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303243</t>
+          <t>304603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324093</t>
+          <t>323941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174894</t>
+          <t>175250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184702</t>
+          <t>184330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484002</t>
+          <t>484722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507002</t>
+          <t>507180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20177</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38130</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>229792</t>
+          <t>230179</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245624</t>
+          <t>246404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122910</t>
+          <t>123100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130339</t>
+          <t>130625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357110</t>
+          <t>356710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375063</t>
+          <t>373882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>363</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>34468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167295</t>
+          <t>167522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178710</t>
+          <t>179229</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264375</t>
+          <t>262874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280040</t>
+          <t>279790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434199</t>
+          <t>432880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>462175</t>
+          <t>462375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88460</t>
+          <t>88146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96264</t>
+          <t>96096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112520</t>
+          <t>112815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122090</t>
+          <t>122025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171136</t>
+          <t>171466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76684</t>
+          <t>76004</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149926</t>
+          <t>147196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231208</t>
+          <t>231696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1399908</t>
+          <t>1399578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1448393</t>
+          <t>1448813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>947684</t>
+          <t>948364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>996272</t>
+          <t>996798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2364205</t>
+          <t>2363717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2445487</t>
+          <t>2448217</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25643</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>48524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>69456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>144260</t>
+          <t>136691</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128514</t>
+          <t>117719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155007</t>
+          <t>149220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85499</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>83138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>102706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>229758</t>
+          <t>231571</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208051</t>
+          <t>209628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243474</t>
+          <t>245198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24206</t>
+          <t>25919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>43896</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24010</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>62158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>205506</t>
+          <t>220047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191571</t>
+          <t>204829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214917</t>
+          <t>231341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>128713</t>
+          <t>137019</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118047</t>
+          <t>127072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134947</t>
+          <t>143675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>334219</t>
+          <t>357066</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318960</t>
+          <t>338804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346713</t>
+          <t>370474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>247971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>247971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>247971</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>370723</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>370723</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>370723</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39083</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32309</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>26502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>255327</t>
+          <t>283100</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243100</t>
+          <t>271589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263790</t>
+          <t>292169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>145361</t>
+          <t>163347</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139603</t>
+          <t>157709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148175</t>
+          <t>166806</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>400688</t>
+          <t>446446</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>388392</t>
+          <t>432297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409680</t>
+          <t>456218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27589</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>54197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>315602</t>
+          <t>323370</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304603</t>
+          <t>311012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>323941</t>
+          <t>332327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>180764</t>
+          <t>199119</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175250</t>
+          <t>193468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184330</t>
+          <t>203452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>496366</t>
+          <t>522489</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484722</t>
+          <t>509497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507180</t>
+          <t>532681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>343191</t>
+          <t>353838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>343191</t>
+          <t>353838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>343191</t>
+          <t>353838</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>189801</t>
+          <t>209856</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>189801</t>
+          <t>209856</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>189801</t>
+          <t>209856</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>532992</t>
+          <t>563694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>532992</t>
+          <t>563694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>532992</t>
+          <t>563694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>238845</t>
+          <t>255767</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230179</t>
+          <t>245784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246404</t>
+          <t>263116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>127561</t>
+          <t>140141</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123100</t>
+          <t>135295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130625</t>
+          <t>143431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>366406</t>
+          <t>395908</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356710</t>
+          <t>384757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373882</t>
+          <t>404326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>279007</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>279007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>279007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>395240</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>395240</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>395240</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,22 +2440,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34468</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>173946</t>
+          <t>190404</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167522</t>
+          <t>183247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179229</t>
+          <t>196138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>276675</t>
+          <t>76964</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262874</t>
+          <t>73684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279790</t>
+          <t>79180</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>450621</t>
+          <t>267368</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>432880</t>
+          <t>259167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>462375</t>
+          <t>273923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>187196</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>187196</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>187196</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>93449</t>
+          <t>101736</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88146</t>
+          <t>96548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96096</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>118531</t>
+          <t>130248</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112815</t>
+          <t>123321</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122025</t>
+          <t>134882</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,69 +3126,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>135843</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171466</t>
+          <t>191270</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>64186</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>50900</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>82942</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>54715</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>27570</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>76004</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>213</t>
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>225668</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147196</t>
+          <t>197117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231696</t>
+          <t>259529</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3239,67 +3239,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1426934</t>
+          <t>1511115</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1399578</t>
+          <t>1481327</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1448813</t>
+          <t>1536754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>839979</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>821223</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>853265</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>90,83%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1132</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>969653</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>948364</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>996798</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2396589</t>
+          <t>2351094</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2363717</t>
+          <t>2317233</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2448217</t>
+          <t>2379645</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
